--- a/ScriptVB/modelo_datas_nao_letivas.xlsx
+++ b/ScriptVB/modelo_datas_nao_letivas.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://enginetecnologia-my.sharepoint.com/personal/ffasti_enginetecnologia_com_br/Documents/Projetos/Claude/Projetos/AlocacaoInstrutores/ScriptVB/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{48637667-916D-46BB-972B-07B4071AA6D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{C594F7C8-5232-4FAC-BEF3-CDA474693B0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{3E70B633-F9CE-421E-8D68-07DF65D4A57B}"/>
+    <workbookView xWindow="1260" yWindow="36" windowWidth="20940" windowHeight="11868" xr2:uid="{770D7732-18F4-4AF9-B03B-6073A1B23417}"/>
   </bookViews>
   <sheets>
     <sheet name="Dados" sheetId="1" r:id="rId1"/>
@@ -503,7 +503,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8BBB127B-706F-49FF-A9B5-D1EC25BBF59B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7AC42945-E05A-48F3-8E31-B4E4C9490B4B}">
   <dimension ref="A1:E9"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
